--- a/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/wilks_importance.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/wilks_importance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,16 +459,6 @@
           <t>LD1 Coefficient</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LD2 Coefficient</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LD3 Coefficient</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -477,43 +467,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1265934215015965</v>
+        <v>0.2520473476683607</v>
       </c>
       <c r="C2" t="n">
-        <v>2.664397547814464</v>
+        <v>12.68391371287738</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08724445870795949</v>
+        <v>0.002083319990712318</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-0.5927666391450778</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.7984787360547143</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.4264764833650512</v>
+        <v>3.995826992211078</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02605768966815525</v>
+        <v>0.0417243639974007</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5484332726773451</v>
+        <v>2.099717523566511</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5839361052783966</v>
+        <v>0.1636309069428076</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -521,29 +505,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-0.5059232488872449</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.007530542705120141</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1836026523848068</v>
+        <v>-1.193139284634939</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01850694798292629</v>
+        <v>0.03823244176269458</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3895136590696919</v>
+        <v>1.923991650127176</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6809996342320495</v>
+        <v>0.1814753472927976</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -551,29 +529,23 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-0.0431953255295802</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.2128152545149326</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.1891106413669753</v>
+        <v>1.416193653216698</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01097001594217728</v>
+        <v>0.006610712337308478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2308846955009753</v>
+        <v>0.3326744186866133</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7953273215118044</v>
+        <v>0.5708595993286933</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -581,29 +553,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1672195995162201</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.2071049035978224</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.1055653843546482</v>
+        <v>-0.5235680969020331</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001883263056381201</v>
+        <v>1.268503827428491e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0396368263831811</v>
+        <v>0.0006383559771764813</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9611922652394375</v>
+        <v>0.9801065036037653</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -611,13 +577,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-0.130842298034187</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.01086534112676102</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.04023777209732681</v>
+        <v>-0.02589181980312264</v>
       </c>
     </row>
   </sheetData>
